--- a/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_3310_completo.xlsx
+++ b/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_3310_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1a35ddee3b094c54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd18c15d8aab44c71"/>
   </x:sheets>
 </x:workbook>
 </file>
